--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484742_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484742_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9628</v>
+        <v>2.712</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8003</v>
+        <v>6.4437</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.8376</v>
+        <v>-3.7317</v>
       </c>
       <c r="G2" t="n">
         <v>1.3424</v>
@@ -610,13 +610,13 @@
         <v>2.2644</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.3949</v>
+        <v>-1.6457</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7613</v>
+        <v>-0.1179</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.6335</v>
+        <v>-1.5277</v>
       </c>
       <c r="V2" t="n">
         <v>1.5056</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.4265</v>
+        <v>-1.4001</v>
       </c>
       <c r="E3" t="n">
         <v>-0.1176</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.309</v>
+        <v>-1.2825</v>
       </c>
       <c r="G3" t="n">
         <v>-1.3266</v>
@@ -688,13 +688,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0999</v>
+        <v>-0.0735</v>
       </c>
       <c r="T3" t="n">
         <v>-0.1176</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0176</v>
+        <v>0.0441</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. BLEDA MIRANDA</t>
+          <t>J. MUNOZ PALENCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-3.5178</v>
+        <v>-3.6788</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.542</v>
+        <v>-1.9203</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9759</v>
+        <v>-1.7586</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.7669</v>
+        <v>0.0537</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.2648</v>
+        <v>0.2293</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5021</v>
+        <v>-0.1756</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.8242</v>
+        <v>0.3195</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.9064</v>
+        <v>0.3436</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0823</v>
+        <v>-0.0241</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9428</v>
+        <v>-0.2657</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3584</v>
+        <v>-0.1143</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5843</v>
+        <v>-0.1515</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.7548</v>
+        <v>-1.887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1322</v>
+        <v>-1.887</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5132</v>
+        <v>-0.3627</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4144</v>
+        <v>-0.3527</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.9276</v>
+        <v>-0.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5171</v>
+        <v>-1.4829</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5171</v>
+        <v>-1.4829</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MUNOZ PALENCIA</t>
+          <t>A. JAQUET</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.6524</v>
+        <v>-3.722</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9203</v>
+        <v>-1.9005</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.7321</v>
+        <v>-1.8214</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0537</v>
+        <v>-2.7219</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2293</v>
+        <v>-0.9422</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1756</v>
+        <v>-1.7796</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3195</v>
+        <v>-1.8664</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3436</v>
+        <v>-0.6496</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0241</v>
+        <v>-1.2169</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2657</v>
+        <v>-0.8555</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1143</v>
+        <v>-0.2927</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1515</v>
+        <v>-0.5628</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.887</v>
+        <v>-0.1887</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3362</v>
+        <v>0.2451</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3527</v>
+        <v>0.1546</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0165</v>
+        <v>0.0905</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.4829</v>
+        <v>-1.2452</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.4829</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. JAQUET</t>
+          <t>C. BLEDA MIRANDA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.0323</v>
+        <v>-3.8282</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.2903</v>
+        <v>-2.9317</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7421</v>
+        <v>-0.8965</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.7219</v>
+        <v>-2.7669</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.9422</v>
+        <v>-2.2648</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.7796</v>
+        <v>-0.5021</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.8664</v>
+        <v>-1.8242</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6496</v>
+        <v>-1.9064</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.2169</v>
+        <v>0.0823</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8555</v>
+        <v>-0.9428</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2927</v>
+        <v>-0.3584</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5628</v>
+        <v>-0.5843</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1887</v>
+        <v>-1.1322</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1887</v>
+        <v>0.3774</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.8236</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2352</v>
+        <v>0.0247</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1699</v>
+        <v>-0.8482</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2452</v>
+        <v>0.5171</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2452</v>
+        <v>0.5171</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.2182</v>
+        <v>-4.0271</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1928</v>
+        <v>-0.134</v>
       </c>
       <c r="F7" t="n">
-        <v>-4.0254</v>
+        <v>-3.8931</v>
       </c>
       <c r="G7" t="n">
         <v>-3.7452</v>
@@ -1000,13 +1000,13 @@
         <v>1.1322</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6884</v>
+        <v>-0.4973</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1147</v>
+        <v>-0.0559</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5737</v>
+        <v>-0.4414</v>
       </c>
       <c r="V7" t="n">
         <v>-0.7281</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. TUDELA GARCIA</t>
+          <t>I. DE ANDREA LUNA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.2955</v>
+        <v>-4.3539</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3557</v>
+        <v>-0.1128</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.9398</v>
+        <v>-4.2411</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9971</v>
+        <v>-1.1674</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.9177</v>
+        <v>-1.1027</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9206</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>2.3755</v>
+        <v>0.9235</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1956</v>
+        <v>0.1009</v>
       </c>
       <c r="L8" t="n">
-        <v>2.1799</v>
+        <v>0.8226</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.3726</v>
+        <v>-2.0909</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.1133</v>
+        <v>-1.2036</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2593</v>
+        <v>-0.8873</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.0757</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q8" t="n">
-        <v>-4.1514</v>
+        <v>-1.3209</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0757</v>
+        <v>1.1322</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2869</v>
+        <v>-0.5715</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4202</v>
+        <v>-0.0172</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7071</v>
+        <v>-0.5543</v>
       </c>
       <c r="V8" t="n">
-        <v>0.06419999999999999</v>
+        <v>-2.4262</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X8" t="n">
-        <v>0.06419999999999999</v>
+        <v>-2.7281</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. DE ANDREA LUNA</t>
+          <t>G. TUDELA GARCIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.5307</v>
+        <v>-4.8478</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2102</v>
+        <v>-1.8815</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.3204</v>
+        <v>-2.9663</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1674</v>
+        <v>-1.9971</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1027</v>
+        <v>-3.9177</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.06469999999999999</v>
+        <v>1.9206</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9235</v>
+        <v>2.3755</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1009</v>
+        <v>0.1956</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8226</v>
+        <v>2.1799</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0909</v>
+        <v>-4.3726</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2036</v>
+        <v>-4.1133</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8873</v>
+        <v>-0.2593</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1887</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.3209</v>
+        <v>-4.1514</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1322</v>
+        <v>2.0757</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7483</v>
+        <v>-0.8391999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1147</v>
+        <v>-0.1056</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6337</v>
+        <v>-0.7336</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.4262</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3018</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.7281</v>
+        <v>0.06419999999999999</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.7892</v>
+        <v>-6.6389</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3691</v>
+        <v>-2.2717</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.4201</v>
+        <v>-4.3672</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6459</v>
@@ -1234,13 +1234,13 @@
         <v>2.2644</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1434</v>
+        <v>-0.993</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0646</v>
+        <v>0.162</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.208</v>
+        <v>-1.1551</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8678</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.3429</v>
+        <v>-10.4261</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7733</v>
+        <v>-4.9094</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.5697</v>
+        <v>-5.5167</v>
       </c>
       <c r="G11" t="n">
         <v>-7.477</v>
@@ -1312,13 +1312,13 @@
         <v>1.3209</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3074</v>
+        <v>-1.3906</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0646</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.372</v>
+        <v>-1.3191</v>
       </c>
       <c r="V11" t="n">
         <v>-0.4263</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.6229</v>
+        <v>-10.9609</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4044</v>
+        <v>-4.3456</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.2185</v>
+        <v>-6.6153</v>
       </c>
       <c r="G12" t="n">
         <v>-2.1687</v>
@@ -1390,13 +1390,13 @@
         <v>1.5096</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7894</v>
+        <v>-2.1274</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8789</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9105</v>
+        <v>-1.3073</v>
       </c>
       <c r="V12" t="n">
         <v>-1.0038</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-51.46560000000001</v>
+        <v>-51.1718</v>
       </c>
       <c r="E13" t="n">
-        <v>-14.3754</v>
+        <v>-14.0814</v>
       </c>
       <c r="F13" t="n">
-        <v>-37.0906</v>
+        <v>-37.0904</v>
       </c>
       <c r="G13" t="n">
         <v>-24.6206</v>
@@ -1438,7 +1438,7 @@
         <v>-21.37260000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.2478</v>
+        <v>-3.247800000000001</v>
       </c>
       <c r="J13" t="n">
         <v>4.012700000000001</v>
@@ -1468,16 +1468,16 @@
         <v>12.2655</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.373200000000001</v>
+        <v>-9.0794</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.6113</v>
+        <v>-1.3172</v>
       </c>
       <c r="U13" t="n">
-        <v>-7.7621</v>
+        <v>-7.762099999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-7.0934</v>
+        <v>-7.093400000000001</v>
       </c>
       <c r="W13" t="n">
         <v>5.8672</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.1719</v>
+        <v>15.2186</v>
       </c>
       <c r="E14" t="n">
-        <v>10.0357</v>
+        <v>11.3998</v>
       </c>
       <c r="F14" t="n">
-        <v>4.1362</v>
+        <v>3.8188</v>
       </c>
       <c r="G14" t="n">
         <v>6.121</v>
@@ -1546,13 +1546,13 @@
         <v>3.2079</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2434</v>
+        <v>1.2901</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5291</v>
+        <v>0.835</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7725</v>
+        <v>0.4551</v>
       </c>
       <c r="V14" t="n">
         <v>4.5997</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.9183</v>
+        <v>7.8847</v>
       </c>
       <c r="E15" t="n">
-        <v>5.191</v>
+        <v>5.5807</v>
       </c>
       <c r="F15" t="n">
-        <v>2.7273</v>
+        <v>2.304</v>
       </c>
       <c r="G15" t="n">
         <v>6.5375</v>
@@ -1624,13 +1624,13 @@
         <v>2.6418</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9277</v>
+        <v>0.8942</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0029</v>
+        <v>0.3926</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9248</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2452</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>R. MALLIK BOUNAD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.9177</v>
+        <v>6.6439</v>
       </c>
       <c r="E16" t="n">
-        <v>5.1088</v>
+        <v>5.2261</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8089</v>
+        <v>1.4177</v>
       </c>
       <c r="G16" t="n">
-        <v>2.4906</v>
+        <v>4.5451</v>
       </c>
       <c r="H16" t="n">
-        <v>2.6741</v>
+        <v>5.9501</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1836</v>
+        <v>-1.4049</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0269</v>
+        <v>6.1649</v>
       </c>
       <c r="K16" t="n">
-        <v>2.8212</v>
+        <v>6.6826</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2057</v>
+        <v>-0.5177</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5363</v>
+        <v>-1.6198</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1471</v>
+        <v>-0.7325</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3892</v>
+        <v>-0.8873</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1322</v>
+        <v>0.9435</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0757</v>
+        <v>1.887</v>
       </c>
       <c r="S16" t="n">
-        <v>1.8083</v>
+        <v>0.8345</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4784</v>
+        <v>0.6463</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3299</v>
+        <v>0.1882</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4866</v>
+        <v>0.3208</v>
       </c>
       <c r="W16" t="n">
-        <v>1.547</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.0604</v>
+        <v>0.9624</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>6.8827</v>
+        <v>5.7782</v>
       </c>
       <c r="E17" t="n">
-        <v>6.6112</v>
+        <v>4.514</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2716</v>
+        <v>1.2642</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5103</v>
+        <v>4.4998</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9283</v>
+        <v>3.1249</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.418</v>
+        <v>1.3749</v>
       </c>
       <c r="J17" t="n">
-        <v>2.6713</v>
+        <v>4.6145</v>
       </c>
       <c r="K17" t="n">
-        <v>2.5309</v>
+        <v>3.175</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1404</v>
+        <v>1.4396</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.161</v>
+        <v>-0.1148</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6026</v>
+        <v>-0.0501</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5584</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5661</v>
+        <v>1.3209</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4531</v>
+        <v>2.2644</v>
       </c>
       <c r="S17" t="n">
-        <v>3.9385</v>
+        <v>1.8444</v>
       </c>
       <c r="T17" t="n">
-        <v>3.9591</v>
+        <v>1.4846</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0205</v>
+        <v>0.3598</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8678</v>
+        <v>-1.8868</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8678</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. MALLIK BOUNAD</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>6.2973</v>
+        <v>5.7414</v>
       </c>
       <c r="E18" t="n">
-        <v>4.6415</v>
+        <v>4.3293</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6558</v>
+        <v>1.4121</v>
       </c>
       <c r="G18" t="n">
-        <v>4.5451</v>
+        <v>2.4906</v>
       </c>
       <c r="H18" t="n">
-        <v>5.9501</v>
+        <v>2.6741</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4049</v>
+        <v>-0.1836</v>
       </c>
       <c r="J18" t="n">
-        <v>6.1649</v>
+        <v>3.0269</v>
       </c>
       <c r="K18" t="n">
-        <v>6.6826</v>
+        <v>2.8212</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5177</v>
+        <v>0.2057</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6198</v>
+        <v>-0.5363</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7325</v>
+        <v>-0.1471</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8873</v>
+        <v>-0.3892</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9435</v>
+        <v>1.1322</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.9435</v>
       </c>
       <c r="R18" t="n">
-        <v>1.887</v>
+        <v>2.0757</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4879</v>
+        <v>0.632</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0617</v>
+        <v>0.6989</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4263</v>
+        <v>-0.0669</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3208</v>
+        <v>1.4866</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6415999999999999</v>
+        <v>1.547</v>
       </c>
       <c r="X18" t="n">
-        <v>0.9624</v>
+        <v>-0.0604</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>P. SILLA TEBAR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>6.1248</v>
+        <v>5.2133</v>
       </c>
       <c r="E19" t="n">
-        <v>5.0986</v>
+        <v>1.8383</v>
       </c>
       <c r="F19" t="n">
-        <v>1.0262</v>
+        <v>3.3749</v>
       </c>
       <c r="G19" t="n">
-        <v>4.4998</v>
+        <v>2.1197</v>
       </c>
       <c r="H19" t="n">
-        <v>3.1249</v>
+        <v>1.7992</v>
       </c>
       <c r="I19" t="n">
-        <v>1.3749</v>
+        <v>0.3205</v>
       </c>
       <c r="J19" t="n">
-        <v>4.6145</v>
+        <v>1.4054</v>
       </c>
       <c r="K19" t="n">
-        <v>3.175</v>
+        <v>1.2154</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4396</v>
+        <v>0.1901</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1148</v>
+        <v>0.7143</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0501</v>
+        <v>0.5838</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.1304</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3209</v>
+        <v>0.7548</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R19" t="n">
-        <v>2.2644</v>
+        <v>2.6418</v>
       </c>
       <c r="S19" t="n">
-        <v>2.1909</v>
+        <v>0.5089</v>
       </c>
       <c r="T19" t="n">
-        <v>2.0692</v>
+        <v>0.4901</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1217</v>
+        <v>0.0189</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8868</v>
+        <v>1.8298</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6415999999999999</v>
+        <v>1.8298</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. SILLA TEBAR</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>4.3029</v>
+        <v>4.9076</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3512</v>
+        <v>4.6625</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9517</v>
+        <v>0.2451</v>
       </c>
       <c r="G20" t="n">
-        <v>2.1197</v>
+        <v>0.5103</v>
       </c>
       <c r="H20" t="n">
-        <v>1.7992</v>
+        <v>1.9283</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3205</v>
+        <v>-1.418</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4054</v>
+        <v>2.6713</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2154</v>
+        <v>2.5309</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1901</v>
+        <v>0.1404</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7143</v>
+        <v>-2.161</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5838</v>
+        <v>-0.6026</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1304</v>
+        <v>-1.5584</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7548</v>
+        <v>0.5661</v>
       </c>
       <c r="Q20" t="n">
         <v>-1.887</v>
       </c>
       <c r="R20" t="n">
-        <v>2.6418</v>
+        <v>2.4531</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4015</v>
+        <v>1.9634</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0029</v>
+        <v>2.0104</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4044</v>
+        <v>-0.047</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8298</v>
+        <v>1.8678</v>
       </c>
       <c r="W20" t="n">
-        <v>1.8298</v>
+        <v>1.8678</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.0735</v>
+        <v>2.5858</v>
       </c>
       <c r="E21" t="n">
-        <v>1.9158</v>
+        <v>2.1107</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1576</v>
+        <v>0.4751</v>
       </c>
       <c r="G21" t="n">
         <v>-3.309</v>
@@ -2092,13 +2092,13 @@
         <v>2.0757</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2733</v>
+        <v>0.7856</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.9061</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4379</v>
+        <v>-0.1205</v>
       </c>
       <c r="V21" t="n">
         <v>4.9204</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4019</v>
+        <v>0.1369</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0301</v>
+        <v>0.1647</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3718</v>
+        <v>-0.0278</v>
       </c>
       <c r="G22" t="n">
         <v>0.6329</v>
@@ -2170,13 +2170,13 @@
         <v>1.6983</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1822</v>
+        <v>0.3565</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0559</v>
+        <v>0.139</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1264</v>
+        <v>0.2176</v>
       </c>
       <c r="V22" t="n">
         <v>-1.6074</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.8214</v>
+        <v>-2.6446</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8331</v>
+        <v>-2.7356</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0117</v>
+        <v>0.091</v>
       </c>
       <c r="G23" t="n">
         <v>0.4726</v>
@@ -2248,13 +2248,13 @@
         <v>1.6983</v>
       </c>
       <c r="S23" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.2638</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0617</v>
+        <v>0.1591</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0253</v>
+        <v>0.1047</v>
       </c>
       <c r="V23" t="n">
         <v>-3.1923</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>51.46580000000002</v>
+        <v>51.4658</v>
       </c>
       <c r="E24" t="n">
-        <v>37.0906</v>
+        <v>37.09050000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>14.3752</v>
+        <v>14.3751</v>
       </c>
       <c r="G24" t="n">
         <v>24.6205</v>
@@ -2296,7 +2296,7 @@
         <v>21.3726</v>
       </c>
       <c r="I24" t="n">
-        <v>3.247800000000001</v>
+        <v>3.2478</v>
       </c>
       <c r="J24" t="n">
         <v>28.6333</v>
@@ -2326,13 +2326,13 @@
         <v>22.644</v>
       </c>
       <c r="S24" t="n">
-        <v>9.3733</v>
+        <v>9.3734</v>
       </c>
       <c r="T24" t="n">
-        <v>7.762099999999999</v>
+        <v>7.7621</v>
       </c>
       <c r="U24" t="n">
-        <v>1.6113</v>
+        <v>1.6114</v>
       </c>
       <c r="V24" t="n">
         <v>7.093400000000001</v>
